--- a/Team-Data/2012-13/2-12-2012-13.xlsx
+++ b/Team-Data/2012-13/2-12-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,13 +806,13 @@
         <v>0.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AF2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
@@ -811,7 +878,7 @@
         <v>24</v>
       </c>
       <c r="BB2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC2" t="n">
         <v>13</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AE3" t="n">
         <v>15</v>
@@ -930,7 +997,7 @@
         <v>13</v>
       </c>
       <c r="AG3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH3" t="n">
         <v>1</v>
@@ -957,13 +1024,13 @@
         <v>16</v>
       </c>
       <c r="AP3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ3" t="n">
         <v>6</v>
       </c>
       <c r="AR3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS3" t="n">
         <v>11</v>
@@ -978,7 +1045,7 @@
         <v>9</v>
       </c>
       <c r="AW3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX3" t="n">
         <v>25</v>
@@ -990,7 +1057,7 @@
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB3" t="n">
         <v>18</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
@@ -1103,16 +1170,16 @@
         <v>0.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE4" t="n">
         <v>9</v>
       </c>
       <c r="AF4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH4" t="n">
         <v>9</v>
@@ -1124,7 +1191,7 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
         <v>11</v>
@@ -1157,10 +1224,10 @@
         <v>29</v>
       </c>
       <c r="AV4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX4" t="n">
         <v>20</v>
@@ -1175,7 +1242,7 @@
         <v>7</v>
       </c>
       <c r="BB4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC4" t="n">
         <v>12</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-8.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1303,7 +1370,7 @@
         <v>30</v>
       </c>
       <c r="AJ5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK5" t="n">
         <v>30</v>
@@ -1327,13 +1394,13 @@
         <v>19</v>
       </c>
       <c r="AR5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU5" t="n">
         <v>30</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>1.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AE6" t="n">
         <v>9</v>
@@ -1479,7 +1546,7 @@
         <v>9</v>
       </c>
       <c r="AH6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI6" t="n">
         <v>25</v>
@@ -1488,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="AK6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL6" t="n">
         <v>29</v>
@@ -1539,7 +1606,7 @@
         <v>12</v>
       </c>
       <c r="BB6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
@@ -1649,13 +1716,13 @@
         <v>-4.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE7" t="n">
         <v>27</v>
       </c>
       <c r="AF7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG7" t="n">
         <v>27</v>
@@ -1664,7 +1731,7 @@
         <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AJ7" t="n">
         <v>3</v>
@@ -1688,7 +1755,7 @@
         <v>13</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR7" t="n">
         <v>8</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>-1.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AE8" t="n">
         <v>19</v>
@@ -1876,7 +1943,7 @@
         <v>26</v>
       </c>
       <c r="AS8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
         <v>15</v>
@@ -1903,7 +1970,7 @@
         <v>20</v>
       </c>
       <c r="BB8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC8" t="n">
         <v>19</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
@@ -1935,52 +2002,52 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E9" t="n">
         <v>33</v>
       </c>
       <c r="F9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G9" t="n">
-        <v>0.623</v>
+        <v>0.635</v>
       </c>
       <c r="H9" t="n">
         <v>48.7</v>
       </c>
       <c r="I9" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="J9" t="n">
         <v>85.59999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.471</v>
+        <v>0.47</v>
       </c>
       <c r="L9" t="n">
         <v>6.5</v>
       </c>
       <c r="M9" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="N9" t="n">
         <v>0.338</v>
       </c>
       <c r="O9" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="P9" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="S9" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="T9" t="n">
         <v>45.8</v>
@@ -1992,10 +2059,10 @@
         <v>15.5</v>
       </c>
       <c r="W9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X9" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="Y9" t="n">
         <v>6.8</v>
@@ -2010,10 +2077,10 @@
         <v>105</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
         <v>5</v>
@@ -2070,7 +2137,7 @@
         <v>28</v>
       </c>
       <c r="AW9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX9" t="n">
         <v>3</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-1.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="n">
         <v>21</v>
@@ -2204,10 +2271,10 @@
         <v>23</v>
       </c>
       <c r="AG10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI10" t="n">
         <v>20</v>
@@ -2228,7 +2295,7 @@
         <v>11</v>
       </c>
       <c r="AO10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E11" t="n">
         <v>30</v>
       </c>
       <c r="F11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G11" t="n">
-        <v>0.577</v>
+        <v>0.588</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
@@ -2329,28 +2396,28 @@
         <v>19.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0.393</v>
+        <v>0.392</v>
       </c>
       <c r="O11" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P11" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.798</v>
+        <v>0.799</v>
       </c>
       <c r="R11" t="n">
         <v>11</v>
       </c>
       <c r="S11" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="T11" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="U11" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="V11" t="n">
         <v>15.2</v>
@@ -2371,25 +2438,25 @@
         <v>19.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>101</v>
+        <v>100.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AE11" t="n">
         <v>9</v>
       </c>
       <c r="AF11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI11" t="n">
         <v>8</v>
@@ -2410,16 +2477,16 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ11" t="n">
         <v>2</v>
       </c>
       <c r="AR11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AS11" t="n">
         <v>1</v>
@@ -2449,7 +2516,7 @@
         <v>23</v>
       </c>
       <c r="BB11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC11" t="n">
         <v>15</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F12" t="n">
         <v>25</v>
       </c>
       <c r="G12" t="n">
-        <v>0.537</v>
+        <v>0.528</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="J12" t="n">
-        <v>83.09999999999999</v>
+        <v>83</v>
       </c>
       <c r="K12" t="n">
         <v>0.462</v>
@@ -2508,10 +2575,10 @@
         <v>10.3</v>
       </c>
       <c r="M12" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.364</v>
+        <v>0.366</v>
       </c>
       <c r="O12" t="n">
         <v>19.1</v>
@@ -2520,22 +2587,22 @@
         <v>25.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="R12" t="n">
         <v>10.9</v>
       </c>
       <c r="S12" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="T12" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="U12" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="V12" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="W12" t="n">
         <v>8.4</v>
@@ -2550,16 +2617,16 @@
         <v>20.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>106.3</v>
+        <v>106.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
         <v>12</v>
@@ -2568,7 +2635,7 @@
         <v>15</v>
       </c>
       <c r="AG12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH12" t="n">
         <v>24</v>
@@ -2589,7 +2656,7 @@
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO12" t="n">
         <v>3</v>
@@ -2598,25 +2665,25 @@
         <v>5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AR12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS12" t="n">
         <v>8</v>
       </c>
       <c r="AT12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV12" t="n">
         <v>30</v>
       </c>
       <c r="AW12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AX12" t="n">
         <v>27</v>
@@ -2631,7 +2698,7 @@
         <v>16</v>
       </c>
       <c r="BB12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC12" t="n">
         <v>8</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>2.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE13" t="n">
         <v>8</v>
@@ -2786,7 +2853,7 @@
         <v>4</v>
       </c>
       <c r="AS13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT13" t="n">
         <v>2</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
@@ -2968,16 +3035,16 @@
         <v>13</v>
       </c>
       <c r="AS14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AT14" t="n">
         <v>16</v>
       </c>
       <c r="AU14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F15" t="n">
         <v>28</v>
       </c>
       <c r="G15" t="n">
-        <v>0.472</v>
+        <v>0.462</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
@@ -3054,61 +3121,61 @@
         <v>8.6</v>
       </c>
       <c r="M15" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0.352</v>
+        <v>0.353</v>
       </c>
       <c r="O15" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="P15" t="n">
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.694</v>
       </c>
       <c r="R15" t="n">
         <v>11.7</v>
       </c>
       <c r="S15" t="n">
-        <v>33.1</v>
+        <v>33</v>
       </c>
       <c r="T15" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
       <c r="U15" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="V15" t="n">
         <v>15.3</v>
       </c>
       <c r="W15" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X15" t="n">
         <v>5.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z15" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AA15" t="n">
         <v>22.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>101.6</v>
+        <v>101.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AF15" t="n">
         <v>18</v>
@@ -3135,7 +3202,7 @@
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO15" t="n">
         <v>4</v>
@@ -3156,7 +3223,7 @@
         <v>3</v>
       </c>
       <c r="AU15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV15" t="n">
         <v>25</v>
@@ -3165,10 +3232,10 @@
         <v>23</v>
       </c>
       <c r="AX15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ15" t="n">
         <v>5</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
@@ -3209,70 +3276,70 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F16" t="n">
         <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>0.647</v>
+        <v>0.64</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J16" t="n">
-        <v>82.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.44</v>
+        <v>0.438</v>
       </c>
       <c r="L16" t="n">
         <v>4.7</v>
       </c>
       <c r="M16" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="N16" t="n">
-        <v>0.345</v>
+        <v>0.343</v>
       </c>
       <c r="O16" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="P16" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.792</v>
+        <v>0.791</v>
       </c>
       <c r="R16" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="S16" t="n">
         <v>29.2</v>
       </c>
       <c r="T16" t="n">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
       <c r="U16" t="n">
         <v>20.9</v>
       </c>
       <c r="V16" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W16" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="X16" t="n">
         <v>5.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z16" t="n">
         <v>19.8</v>
@@ -3281,16 +3348,16 @@
         <v>19.6</v>
       </c>
       <c r="AB16" t="n">
-        <v>93.7</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AE16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF16" t="n">
         <v>6</v>
@@ -3302,13 +3369,13 @@
         <v>16</v>
       </c>
       <c r="AI16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ16" t="n">
         <v>11</v>
       </c>
       <c r="AK16" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO16" t="n">
         <v>22</v>
@@ -3326,13 +3393,13 @@
         <v>24</v>
       </c>
       <c r="AQ16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR16" t="n">
         <v>2</v>
       </c>
       <c r="AS16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT16" t="n">
         <v>13</v>
@@ -3341,7 +3408,7 @@
         <v>23</v>
       </c>
       <c r="AV16" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AW16" t="n">
         <v>2</v>
@@ -3350,16 +3417,16 @@
         <v>14</v>
       </c>
       <c r="AY16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA16" t="n">
         <v>18</v>
       </c>
       <c r="BB16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC16" t="n">
         <v>7</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
@@ -3391,28 +3458,28 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F17" t="n">
         <v>14</v>
       </c>
       <c r="G17" t="n">
-        <v>0.714</v>
+        <v>0.708</v>
       </c>
       <c r="H17" t="n">
         <v>48.6</v>
       </c>
       <c r="I17" t="n">
-        <v>38.8</v>
+        <v>38.7</v>
       </c>
       <c r="J17" t="n">
-        <v>78.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.494</v>
+        <v>0.492</v>
       </c>
       <c r="L17" t="n">
         <v>8.1</v>
@@ -3424,52 +3491,52 @@
         <v>0.386</v>
       </c>
       <c r="O17" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="P17" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.76</v>
+        <v>0.758</v>
       </c>
       <c r="R17" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="S17" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="T17" t="n">
-        <v>38.7</v>
+        <v>38.9</v>
       </c>
       <c r="U17" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="V17" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W17" t="n">
         <v>8.4</v>
       </c>
       <c r="X17" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Z17" t="n">
         <v>19.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>103.1</v>
+        <v>102.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE17" t="n">
         <v>4</v>
@@ -3499,7 +3566,7 @@
         <v>9</v>
       </c>
       <c r="AN17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO17" t="n">
         <v>10</v>
@@ -3508,13 +3575,13 @@
         <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
@@ -3529,13 +3596,13 @@
         <v>9</v>
       </c>
       <c r="AX17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA17" t="n">
         <v>11</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-1.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
@@ -3675,13 +3742,13 @@
         <v>26</v>
       </c>
       <c r="AL18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM18" t="n">
         <v>19</v>
       </c>
       <c r="AN18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO18" t="n">
         <v>23</v>
@@ -3696,7 +3763,7 @@
         <v>3</v>
       </c>
       <c r="AS18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT18" t="n">
         <v>7</v>
@@ -3711,7 +3778,7 @@
         <v>6</v>
       </c>
       <c r="AX18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY18" t="n">
         <v>8</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3903,7 @@
         <v>28</v>
       </c>
       <c r="AE19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF19" t="n">
         <v>21</v>
@@ -3854,7 +3921,7 @@
         <v>21</v>
       </c>
       <c r="AK19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL19" t="n">
         <v>28</v>
@@ -3878,10 +3945,10 @@
         <v>5</v>
       </c>
       <c r="AS19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU19" t="n">
         <v>18</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
@@ -4015,19 +4082,19 @@
         <v>-3.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE20" t="n">
         <v>25</v>
       </c>
       <c r="AF20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG20" t="n">
         <v>25</v>
       </c>
       <c r="AH20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI20" t="n">
         <v>24</v>
@@ -4069,7 +4136,7 @@
         <v>22</v>
       </c>
       <c r="AV20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW20" t="n">
         <v>29</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4267,7 @@
         <v>28</v>
       </c>
       <c r="AE21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF21" t="n">
         <v>4</v>
@@ -4239,13 +4306,13 @@
         <v>18</v>
       </c>
       <c r="AR21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS21" t="n">
         <v>22</v>
       </c>
       <c r="AT21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU21" t="n">
         <v>27</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E22" t="n">
         <v>39</v>
       </c>
       <c r="F22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G22" t="n">
-        <v>0.75</v>
+        <v>0.765</v>
       </c>
       <c r="H22" t="n">
         <v>48.5</v>
@@ -4319,79 +4386,79 @@
         <v>38.2</v>
       </c>
       <c r="J22" t="n">
-        <v>79.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.482</v>
+        <v>0.481</v>
       </c>
       <c r="L22" t="n">
         <v>7.7</v>
       </c>
       <c r="M22" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="N22" t="n">
-        <v>0.391</v>
+        <v>0.392</v>
       </c>
       <c r="O22" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="P22" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.825</v>
+        <v>0.829</v>
       </c>
       <c r="R22" t="n">
         <v>10.3</v>
       </c>
       <c r="S22" t="n">
-        <v>32.6</v>
+        <v>32.9</v>
       </c>
       <c r="T22" t="n">
-        <v>42.9</v>
+        <v>43.2</v>
       </c>
       <c r="U22" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="V22" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="W22" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="X22" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="Y22" t="n">
         <v>4.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA22" t="n">
         <v>20.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>106.2</v>
+        <v>106.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.1</v>
+        <v>9.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG22" t="n">
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI22" t="n">
         <v>5</v>
@@ -4424,13 +4491,13 @@
         <v>25</v>
       </c>
       <c r="AS22" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AT22" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AU22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV22" t="n">
         <v>29</v>
@@ -4439,7 +4506,7 @@
         <v>7</v>
       </c>
       <c r="AX22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY22" t="n">
         <v>4</v>
@@ -4448,10 +4515,10 @@
         <v>18</v>
       </c>
       <c r="BA22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
@@ -4561,13 +4628,13 @@
         <v>-4.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AE23" t="n">
         <v>28</v>
       </c>
       <c r="AF23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG23" t="n">
         <v>29</v>
@@ -4582,7 +4649,7 @@
         <v>7</v>
       </c>
       <c r="AK23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL23" t="n">
         <v>17</v>
@@ -4591,7 +4658,7 @@
         <v>15</v>
       </c>
       <c r="AN23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO23" t="n">
         <v>29</v>
@@ -4600,7 +4667,7 @@
         <v>30</v>
       </c>
       <c r="AQ23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR23" t="n">
         <v>24</v>
@@ -4615,7 +4682,7 @@
         <v>5</v>
       </c>
       <c r="AV23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW23" t="n">
         <v>30</v>
@@ -4624,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="AY23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ23" t="n">
         <v>8</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-3.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE24" t="n">
         <v>19</v>
@@ -4764,7 +4831,7 @@
         <v>5</v>
       </c>
       <c r="AK24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL24" t="n">
         <v>22</v>
@@ -4785,7 +4852,7 @@
         <v>25</v>
       </c>
       <c r="AR24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS24" t="n">
         <v>15</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E25" t="n">
         <v>17</v>
       </c>
       <c r="F25" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G25" t="n">
-        <v>0.321</v>
+        <v>0.327</v>
       </c>
       <c r="H25" t="n">
         <v>48.3</v>
@@ -4871,37 +4938,37 @@
         <v>0.443</v>
       </c>
       <c r="L25" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="M25" t="n">
         <v>17.4</v>
       </c>
       <c r="N25" t="n">
-        <v>0.325</v>
+        <v>0.326</v>
       </c>
       <c r="O25" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="P25" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.754</v>
+        <v>0.755</v>
       </c>
       <c r="R25" t="n">
         <v>11.3</v>
       </c>
       <c r="S25" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T25" t="n">
-        <v>41</v>
+        <v>40.8</v>
       </c>
       <c r="U25" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V25" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W25" t="n">
         <v>7.7</v>
@@ -4916,22 +4983,22 @@
         <v>20.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>94.7</v>
+        <v>94.8</v>
       </c>
       <c r="AC25" t="n">
         <v>-5.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
         <v>26</v>
       </c>
       <c r="AF25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG25" t="n">
         <v>26</v>
@@ -4946,7 +5013,7 @@
         <v>6</v>
       </c>
       <c r="AK25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL25" t="n">
         <v>26</v>
@@ -4970,16 +5037,16 @@
         <v>16</v>
       </c>
       <c r="AS25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT25" t="n">
         <v>24</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>22</v>
       </c>
       <c r="AU25" t="n">
         <v>19</v>
       </c>
       <c r="AV25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AW25" t="n">
         <v>17</v>
@@ -4997,7 +5064,7 @@
         <v>28</v>
       </c>
       <c r="BB25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC25" t="n">
         <v>28</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
@@ -5029,28 +5096,28 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E26" t="n">
         <v>25</v>
       </c>
       <c r="F26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G26" t="n">
-        <v>0.481</v>
+        <v>0.49</v>
       </c>
       <c r="H26" t="n">
         <v>48.7</v>
       </c>
       <c r="I26" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J26" t="n">
-        <v>82</v>
+        <v>82.2</v>
       </c>
       <c r="K26" t="n">
-        <v>0.444</v>
+        <v>0.442</v>
       </c>
       <c r="L26" t="n">
         <v>8.199999999999999</v>
@@ -5068,31 +5135,31 @@
         <v>21.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.776</v>
+        <v>0.774</v>
       </c>
       <c r="R26" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="S26" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="T26" t="n">
-        <v>41.6</v>
+        <v>41.9</v>
       </c>
       <c r="U26" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="V26" t="n">
         <v>15</v>
       </c>
       <c r="W26" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z26" t="n">
         <v>18.7</v>
@@ -5101,13 +5168,13 @@
         <v>19.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>97.3</v>
+        <v>97.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.4</v>
+        <v>-2.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AE26" t="n">
         <v>16</v>
@@ -5122,13 +5189,13 @@
         <v>5</v>
       </c>
       <c r="AI26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ26" t="n">
         <v>15</v>
       </c>
       <c r="AK26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AL26" t="n">
         <v>6</v>
@@ -5140,22 +5207,22 @@
         <v>26</v>
       </c>
       <c r="AO26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP26" t="n">
         <v>21</v>
       </c>
       <c r="AQ26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS26" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AT26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU26" t="n">
         <v>21</v>
@@ -5164,7 +5231,7 @@
         <v>20</v>
       </c>
       <c r="AW26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX26" t="n">
         <v>21</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E27" t="n">
         <v>19</v>
       </c>
       <c r="F27" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G27" t="n">
-        <v>0.358</v>
+        <v>0.365</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
@@ -5232,16 +5299,16 @@
         <v>83.09999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L27" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="M27" t="n">
         <v>18.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0.352</v>
+        <v>0.354</v>
       </c>
       <c r="O27" t="n">
         <v>17.2</v>
@@ -5250,16 +5317,16 @@
         <v>22.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.754</v>
+        <v>0.755</v>
       </c>
       <c r="R27" t="n">
         <v>12</v>
       </c>
       <c r="S27" t="n">
-        <v>28.3</v>
+        <v>28.4</v>
       </c>
       <c r="T27" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="U27" t="n">
         <v>19.8</v>
@@ -5271,37 +5338,37 @@
         <v>8.4</v>
       </c>
       <c r="X27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AA27" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AB27" t="n">
-        <v>96.8</v>
+        <v>96.7</v>
       </c>
       <c r="AC27" t="n">
         <v>-6.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF27" t="n">
         <v>23</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>24</v>
       </c>
       <c r="AG27" t="n">
         <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI27" t="n">
         <v>19</v>
@@ -5310,16 +5377,16 @@
         <v>9</v>
       </c>
       <c r="AK27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL27" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AM27" t="n">
         <v>20</v>
       </c>
       <c r="AN27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO27" t="n">
         <v>12</v>
@@ -5328,7 +5395,7 @@
         <v>12</v>
       </c>
       <c r="AQ27" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AR27" t="n">
         <v>11</v>
@@ -5346,7 +5413,7 @@
         <v>19</v>
       </c>
       <c r="AW27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX27" t="n">
         <v>24</v>
@@ -5358,10 +5425,10 @@
         <v>25</v>
       </c>
       <c r="BA27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>8.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5483,7 +5550,7 @@
         <v>1</v>
       </c>
       <c r="AH28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI28" t="n">
         <v>2</v>
@@ -5501,7 +5568,7 @@
         <v>6</v>
       </c>
       <c r="AN28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO28" t="n">
         <v>19</v>
@@ -5510,7 +5577,7 @@
         <v>22</v>
       </c>
       <c r="AQ28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
@@ -5531,7 +5598,7 @@
         <v>3</v>
       </c>
       <c r="AX28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F29" t="n">
         <v>32</v>
       </c>
       <c r="G29" t="n">
-        <v>0.385</v>
+        <v>0.373</v>
       </c>
       <c r="H29" t="n">
         <v>49</v>
@@ -5599,28 +5666,28 @@
         <v>0.444</v>
       </c>
       <c r="L29" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M29" t="n">
         <v>21.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0.351</v>
+        <v>0.348</v>
       </c>
       <c r="O29" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P29" t="n">
         <v>22.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.775</v>
+        <v>0.772</v>
       </c>
       <c r="R29" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S29" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="T29" t="n">
         <v>40.2</v>
@@ -5632,10 +5699,10 @@
         <v>13</v>
       </c>
       <c r="W29" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X29" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y29" t="n">
         <v>5.2</v>
@@ -5647,25 +5714,25 @@
         <v>19.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>97.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC29" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AE29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF29" t="n">
         <v>22</v>
       </c>
       <c r="AG29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI29" t="n">
         <v>18</v>
@@ -5683,10 +5750,10 @@
         <v>8</v>
       </c>
       <c r="AN29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP29" t="n">
         <v>16</v>
@@ -5695,10 +5762,10 @@
         <v>10</v>
       </c>
       <c r="AR29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT29" t="n">
         <v>28</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
@@ -5757,34 +5824,34 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F30" t="n">
         <v>24</v>
       </c>
       <c r="G30" t="n">
-        <v>0.547</v>
+        <v>0.538</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
       </c>
       <c r="I30" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J30" t="n">
-        <v>81.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L30" t="n">
         <v>6.1</v>
       </c>
       <c r="M30" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="N30" t="n">
         <v>0.365</v>
@@ -5796,46 +5863,46 @@
         <v>24</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.766</v>
+        <v>0.765</v>
       </c>
       <c r="R30" t="n">
         <v>12.2</v>
       </c>
       <c r="S30" t="n">
-        <v>29.6</v>
+        <v>29.8</v>
       </c>
       <c r="T30" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U30" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="V30" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W30" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X30" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Z30" t="n">
         <v>21.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>98.3</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
         <v>12</v>
@@ -5853,19 +5920,19 @@
         <v>17</v>
       </c>
       <c r="AJ30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM30" t="n">
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO30" t="n">
         <v>5</v>
@@ -5880,10 +5947,10 @@
         <v>10</v>
       </c>
       <c r="AS30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU30" t="n">
         <v>8</v>
@@ -5892,7 +5959,7 @@
         <v>18</v>
       </c>
       <c r="AW30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX30" t="n">
         <v>5</v>
@@ -5904,7 +5971,7 @@
         <v>28</v>
       </c>
       <c r="BA30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB30" t="n">
         <v>11</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-3.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
@@ -6041,7 +6108,7 @@
         <v>29</v>
       </c>
       <c r="AL31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM31" t="n">
         <v>18</v>
@@ -6062,7 +6129,7 @@
         <v>23</v>
       </c>
       <c r="AS31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT31" t="n">
         <v>8</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-12-2012-13</t>
+          <t>2013-02-12</t>
         </is>
       </c>
     </row>
